--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T08:08:15+00:00</t>
+    <t>2026-05-18T14:11:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T14:11:29+00:00</t>
+    <t>2026-05-21T09:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T09:18:21+00:00</t>
+    <t>2026-06-01T14:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:41:15+00:00</t>
+    <t>2026-06-01T15:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T15:18:33+00:00</t>
+    <t>2026-06-02T07:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$134</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5194" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4933" uniqueCount="647">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:35:19+00:00</t>
+    <t>2026-06-04T15:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -605,8 +605,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l’entrée. 
- - Attribué par le LPS avec un identifiant unique de type UUID affecté à l’attribut root (l’attribut extension est omis).</t>
+    <t>Identifiant</t>
   </si>
   <si>
     <t>A unique identifier assigned to this immunization record.</t>
@@ -771,19 +770,31 @@
     <t>cis</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:cis.id</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-vaccine-code-cis</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:translation</t>
+  </si>
+  <si>
+    <t>translation</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-medication-translation-document</t>
+  </si>
+  <si>
+    <t>Immunization.vaccineCode.coding:translation.id</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.id</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:cis.extension</t>
+    <t>Immunization.vaccineCode.coding:translation.extension</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.extension</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:cis.system</t>
+    <t>Immunization.vaccineCode.coding:translation.system</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.system</t>
@@ -801,9 +812,6 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-bdpm</t>
-  </si>
-  <si>
     <t>Coding.system</t>
   </si>
   <si>
@@ -813,7 +821,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:cis.version</t>
+    <t>Immunization.vaccineCode.coding:translation.version</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.version</t>
@@ -837,7 +845,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:cis.code</t>
+    <t>Immunization.vaccineCode.coding:translation.code</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.code</t>
@@ -861,7 +869,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:cis.display</t>
+    <t>Immunization.vaccineCode.coding:translation.display</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.display</t>
@@ -885,7 +893,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.coding:cis.userSelected</t>
+    <t>Immunization.vaccineCode.coding:translation.userSelected</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.coding.userSelected</t>
@@ -914,36 +922,6 @@
   </si>
   <si>
     <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation</t>
-  </si>
-  <si>
-    <t>translation</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-medication-translation-document</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.id</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.extension</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.system</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.version</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.code</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.display</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.coding:translation.userSelected</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.text</t>
@@ -2352,7 +2330,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO141"/>
+  <dimension ref="A1:AO134"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="65.6953125" customWidth="true" bestFit="true"/>
@@ -5151,13 +5129,11 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y24" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="Y24" s="2"/>
       <c r="Z24" t="s" s="2">
-        <v>78</v>
+        <v>241</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -5207,12 +5183,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="C25" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="C25" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="D25" t="s" s="2">
         <v>78</v>
       </c>
@@ -5221,7 +5199,7 @@
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>78</v>
@@ -5230,19 +5208,23 @@
         <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>155</v>
+        <v>229</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
+        <v>231</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
       </c>
@@ -5266,13 +5248,11 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
@@ -5290,28 +5270,28 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>158</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>78</v>
+        <v>237</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>159</v>
+        <v>238</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>78</v>
@@ -5322,21 +5302,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -5348,17 +5328,15 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>226</v>
+        <v>156</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5395,31 +5373,31 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -5439,21 +5417,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
@@ -5462,23 +5440,21 @@
         <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -5487,7 +5463,7 @@
         <v>78</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>251</v>
+        <v>78</v>
       </c>
       <c r="T27" t="s" s="2">
         <v>78</v>
@@ -5514,40 +5490,40 @@
         <v>78</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>163</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>254</v>
+        <v>159</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>78</v>
@@ -5558,10 +5534,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5569,7 +5545,7 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>89</v>
@@ -5584,18 +5560,20 @@
         <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>253</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>254</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5643,7 +5621,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5661,10 +5639,10 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5675,10 +5653,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5701,18 +5679,18 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5760,7 +5738,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5778,10 +5756,10 @@
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5792,10 +5770,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5818,17 +5796,17 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5877,7 +5855,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5895,10 +5873,10 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -5909,10 +5887,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5935,19 +5913,17 @@
         <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>281</v>
+        <v>155</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>277</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5996,7 +5972,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -6014,10 +5990,10 @@
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -6028,14 +6004,12 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>78</v>
       </c>
@@ -6044,7 +6018,7 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>78</v>
@@ -6056,19 +6030,19 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>230</v>
+        <v>285</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>232</v>
+        <v>287</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>233</v>
+        <v>288</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
@@ -6093,11 +6067,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>291</v>
+        <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -6115,13 +6091,13 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>236</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>78</v>
@@ -6133,10 +6109,10 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>237</v>
+        <v>290</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>238</v>
+        <v>291</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -6150,7 +6126,7 @@
         <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>242</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6170,19 +6146,23 @@
         <v>78</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
         <v>155</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>156</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
@@ -6230,7 +6210,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>158</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6242,16 +6222,16 @@
         <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>78</v>
+        <v>298</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>159</v>
+        <v>299</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -6262,21 +6242,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>244</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>78</v>
@@ -6285,20 +6265,18 @@
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>134</v>
+        <v>301</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>226</v>
+        <v>302</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -6335,43 +6313,43 @@
         <v>78</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>163</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>159</v>
+        <v>306</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>78</v>
+        <v>307</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -6379,10 +6357,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>246</v>
+        <v>308</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6390,7 +6368,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>89</v>
@@ -6402,23 +6380,19 @@
         <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>103</v>
+        <v>309</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>247</v>
+        <v>310</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>250</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
@@ -6466,7 +6440,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>252</v>
+        <v>308</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6481,27 +6455,27 @@
         <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>253</v>
+        <v>313</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>78</v>
+        <v>315</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>256</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6509,13 +6483,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>78</v>
@@ -6524,16 +6498,16 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>155</v>
+        <v>317</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>258</v>
+        <v>319</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>259</v>
+        <v>320</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6583,10 +6557,10 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>260</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>89</v>
@@ -6598,27 +6572,27 @@
         <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>78</v>
+        <v>321</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>261</v>
+        <v>322</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>262</v>
+        <v>323</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>78</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6638,21 +6612,19 @@
         <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>265</v>
+        <v>327</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>266</v>
+        <v>328</v>
       </c>
       <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>78</v>
       </c>
@@ -6700,7 +6672,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>268</v>
+        <v>158</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6712,16 +6684,16 @@
         <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>269</v>
+        <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6732,10 +6704,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>272</v>
+        <v>329</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6746,7 +6718,7 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>78</v>
@@ -6755,21 +6727,19 @@
         <v>78</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>273</v>
+        <v>135</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>274</v>
+        <v>136</v>
       </c>
       <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>275</v>
-      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>78</v>
       </c>
@@ -6805,40 +6775,38 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="AC38" s="2"/>
       <c r="AD38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>163</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>278</v>
+        <v>78</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6849,12 +6817,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>298</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6872,23 +6842,19 @@
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>281</v>
+        <v>332</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>282</v>
+        <v>333</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>285</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6936,28 +6902,28 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>286</v>
+        <v>163</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>288</v>
+        <v>335</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>78</v>
@@ -6968,10 +6934,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6991,23 +6957,19 @@
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>155</v>
+        <v>317</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>300</v>
+        <v>337</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>303</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
       </c>
@@ -7055,7 +7017,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>304</v>
+        <v>339</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7067,16 +7029,16 @@
         <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>305</v>
+        <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>306</v>
+        <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>78</v>
@@ -7087,10 +7049,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>307</v>
+        <v>340</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>307</v>
+        <v>340</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7098,7 +7060,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>89</v>
@@ -7110,16 +7072,16 @@
         <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>309</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>310</v>
+        <v>342</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7170,10 +7132,10 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>307</v>
+        <v>340</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
@@ -7185,16 +7147,16 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>311</v>
+        <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>312</v>
+        <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>314</v>
+        <v>344</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
@@ -7202,10 +7164,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7225,18 +7187,20 @@
         <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7285,7 +7249,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>315</v>
+        <v>345</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7300,27 +7264,27 @@
         <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>319</v>
+        <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7328,31 +7292,31 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>324</v>
+        <v>205</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7378,13 +7342,13 @@
         <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>78</v>
+        <v>356</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>78</v>
+        <v>357</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -7402,10 +7366,10 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>89</v>
@@ -7417,27 +7381,27 @@
         <v>101</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>328</v>
+        <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>330</v>
+        <v>358</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>332</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7460,13 +7424,13 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>155</v>
+        <v>360</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7517,7 +7481,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>158</v>
+        <v>359</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7529,19 +7493,19 @@
         <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>78</v>
+        <v>363</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>78</v>
+        <v>364</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>78</v>
+        <v>365</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>78</v>
+        <v>366</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -7549,10 +7513,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>367</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7563,7 +7527,7 @@
         <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
@@ -7575,13 +7539,13 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>134</v>
+        <v>368</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>135</v>
+        <v>369</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>136</v>
+        <v>370</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7620,56 +7584,56 @@
         <v>78</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC45" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>163</v>
+        <v>367</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>78</v>
+        <v>373</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C46" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>78</v>
       </c>
@@ -7681,7 +7645,7 @@
         <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>78</v>
@@ -7690,13 +7654,13 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>339</v>
+        <v>155</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>340</v>
+        <v>375</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>341</v>
+        <v>376</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7747,42 +7711,42 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>163</v>
+        <v>374</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>78</v>
+        <v>377</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>78</v>
+        <v>379</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>343</v>
+        <v>380</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7796,7 +7760,7 @@
         <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>78</v>
@@ -7805,13 +7769,13 @@
         <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>324</v>
+        <v>381</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7862,7 +7826,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>346</v>
+        <v>380</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7874,16 +7838,16 @@
         <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>78</v>
+        <v>384</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>78</v>
+        <v>385</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>78</v>
@@ -7892,12 +7856,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7911,7 +7875,7 @@
         <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>78</v>
@@ -7920,13 +7884,13 @@
         <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>324</v>
+        <v>205</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>348</v>
+        <v>387</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7953,13 +7917,11 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>78</v>
+        <v>389</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7977,7 +7939,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>347</v>
+        <v>386</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7995,24 +7957,24 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>78</v>
+        <v>390</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>350</v>
+        <v>391</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>351</v>
+        <v>78</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>78</v>
+        <v>392</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8026,26 +7988,24 @@
         <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>281</v>
+        <v>205</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -8070,13 +8030,11 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>78</v>
+        <v>396</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -8094,7 +8052,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8112,24 +8070,24 @@
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>356</v>
+        <v>397</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>357</v>
+        <v>398</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>358</v>
+        <v>78</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>78</v>
+        <v>399</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8143,7 +8101,7 @@
         <v>89</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>78</v>
@@ -8152,17 +8110,15 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>205</v>
+        <v>401</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>360</v>
+        <v>402</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -8187,13 +8143,13 @@
         <v>78</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>363</v>
+        <v>78</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>364</v>
+        <v>78</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -8211,7 +8167,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8229,24 +8185,24 @@
         <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>356</v>
+        <v>404</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>365</v>
+        <v>405</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>358</v>
+        <v>78</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8257,25 +8213,25 @@
         <v>79</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>367</v>
+        <v>407</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>369</v>
+        <v>409</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8326,13 +8282,13 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>366</v>
+        <v>406</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>78</v>
@@ -8341,16 +8297,16 @@
         <v>101</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>370</v>
+        <v>410</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>371</v>
+        <v>411</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>372</v>
+        <v>412</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>373</v>
+        <v>78</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
@@ -8358,10 +8314,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8384,13 +8340,13 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>375</v>
+        <v>155</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>376</v>
+        <v>156</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>377</v>
+        <v>157</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8441,7 +8397,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>374</v>
+        <v>158</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8453,44 +8409,44 @@
         <v>78</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>378</v>
+        <v>78</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>379</v>
+        <v>159</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>380</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>414</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>78</v>
@@ -8499,15 +8455,17 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>382</v>
+        <v>226</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>78</v>
@@ -8556,74 +8514,78 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>163</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>385</v>
+        <v>159</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>386</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>415</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I54" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I54" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J54" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>388</v>
+        <v>134</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8671,28 +8633,28 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>391</v>
+        <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>392</v>
+        <v>132</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
@@ -8701,12 +8663,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8720,22 +8682,22 @@
         <v>89</v>
       </c>
       <c r="H55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J55" t="s" s="2">
         <v>90</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>205</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8762,11 +8724,13 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="Z55" t="s" s="2">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -8784,7 +8748,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8799,27 +8763,27 @@
         <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>78</v>
+        <v>426</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>398</v>
+        <v>427</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>399</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8827,30 +8791,32 @@
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J56" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K56" t="s" s="2">
-        <v>205</v>
+        <v>429</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>401</v>
+        <v>430</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -8875,11 +8841,13 @@
         <v>78</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y56" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z56" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>78</v>
@@ -8897,10 +8865,10 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>400</v>
+        <v>428</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>89</v>
@@ -8912,27 +8880,27 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>433</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>78</v>
+        <v>435</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>406</v>
+        <v>78</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8946,7 +8914,7 @@
         <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
@@ -8955,13 +8923,13 @@
         <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>408</v>
+        <v>155</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>409</v>
+        <v>156</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>410</v>
+        <v>157</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9012,7 +8980,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>407</v>
+        <v>158</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9024,16 +8992,16 @@
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>411</v>
+        <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>412</v>
+        <v>159</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -9042,12 +9010,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9055,28 +9023,28 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>414</v>
+        <v>134</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>415</v>
+        <v>135</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>416</v>
+        <v>136</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9115,19 +9083,19 @@
         <v>78</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>413</v>
+        <v>163</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9139,16 +9107,16 @@
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>417</v>
+        <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>419</v>
+        <v>78</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -9159,18 +9127,20 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G59" t="s" s="2">
         <v>89</v>
@@ -9185,13 +9155,13 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>155</v>
+        <v>440</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>156</v>
+        <v>441</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>157</v>
+        <v>442</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9242,19 +9212,19 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -9263,7 +9233,7 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9274,21 +9244,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9300,17 +9270,15 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>226</v>
+        <v>156</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9359,19 +9327,19 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -9391,18 +9359,18 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>422</v>
+        <v>445</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>80</v>
@@ -9411,26 +9379,22 @@
         <v>78</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
         <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>424</v>
+        <v>135</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9466,19 +9430,19 @@
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>426</v>
+        <v>163</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9499,7 +9463,7 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -9510,18 +9474,20 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>89</v>
@@ -9533,16 +9499,16 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>428</v>
+        <v>135</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>429</v>
+        <v>136</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9569,13 +9535,13 @@
         <v>78</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>431</v>
+        <v>78</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>432</v>
+        <v>78</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>78</v>
@@ -9593,28 +9559,28 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>427</v>
+        <v>163</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>433</v>
+        <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>434</v>
+        <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -9625,10 +9591,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9636,7 +9602,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>89</v>
@@ -9648,20 +9614,18 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>436</v>
+        <v>155</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>437</v>
+        <v>156</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -9710,10 +9674,10 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>435</v>
+        <v>158</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>89</v>
@@ -9722,19 +9686,19 @@
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>440</v>
+        <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>441</v>
+        <v>159</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9742,10 +9706,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9756,7 +9720,7 @@
         <v>79</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -9768,13 +9732,13 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9813,31 +9777,31 @@
         <v>78</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
@@ -9846,7 +9810,7 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>78</v>
@@ -9857,10 +9821,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9871,7 +9835,7 @@
         <v>89</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>78</v>
@@ -9883,22 +9847,24 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>78</v>
@@ -9928,31 +9894,31 @@
         <v>78</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -9961,7 +9927,7 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9972,20 +9938,18 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>89</v>
@@ -10000,13 +9964,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>447</v>
+        <v>109</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10018,7 +9982,7 @@
         <v>78</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>78</v>
+        <v>460</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>78</v>
@@ -10033,13 +9997,11 @@
         <v>78</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>78</v>
+        <v>461</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>78</v>
@@ -10057,19 +10019,19 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
@@ -10078,7 +10040,7 @@
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -10089,12 +10051,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>78</v>
       </c>
@@ -10115,13 +10079,13 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>156</v>
+        <v>464</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10172,19 +10136,19 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
@@ -10193,7 +10157,7 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
@@ -10204,10 +10168,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10215,10 +10179,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>454</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -10230,13 +10194,13 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10275,31 +10239,31 @@
         <v>78</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
@@ -10308,7 +10272,7 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
@@ -10319,23 +10283,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="C69" t="s" s="2">
-        <v>456</v>
-      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -10392,16 +10354,16 @@
         <v>78</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF69" t="s" s="2">
         <v>163</v>
@@ -10436,10 +10398,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10447,7 +10409,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>89</v>
@@ -10462,22 +10424,24 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>78</v>
@@ -10519,10 +10483,10 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>89</v>
@@ -10540,7 +10504,7 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10551,10 +10515,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10565,7 +10529,7 @@
         <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>78</v>
@@ -10577,13 +10541,13 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>135</v>
+        <v>458</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>136</v>
+        <v>459</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10622,31 +10586,31 @@
         <v>78</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
@@ -10655,7 +10619,7 @@
         <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -10666,12 +10630,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C72" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="C72" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="D72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10692,24 +10658,22 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>78</v>
@@ -10751,19 +10715,19 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AG72" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
@@ -10772,7 +10736,7 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10783,10 +10747,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10809,13 +10773,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>465</v>
+        <v>156</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>466</v>
+        <v>157</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10827,7 +10791,7 @@
         <v>78</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>467</v>
+        <v>78</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>78</v>
@@ -10842,11 +10806,13 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -10864,7 +10830,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10876,7 +10842,7 @@
         <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
@@ -10885,7 +10851,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10896,14 +10862,12 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="C74" t="s" s="2">
-        <v>470</v>
-      </c>
+      <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>78</v>
       </c>
@@ -10912,7 +10876,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10927,7 +10891,7 @@
         <v>134</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>471</v>
+        <v>135</v>
       </c>
       <c r="M74" t="s" s="2">
         <v>136</v>
@@ -10969,16 +10933,16 @@
         <v>78</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF74" t="s" s="2">
         <v>163</v>
@@ -11013,10 +10977,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11024,7 +10988,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>89</v>
@@ -11039,22 +11003,24 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>78</v>
+        <v>470</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>78</v>
@@ -11096,10 +11062,10 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH75" t="s" s="2">
         <v>89</v>
@@ -11117,7 +11083,7 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11128,10 +11094,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11142,7 +11108,7 @@
         <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>78</v>
@@ -11154,13 +11120,13 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>134</v>
+        <v>475</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>135</v>
+        <v>458</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>136</v>
+        <v>459</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11199,31 +11165,31 @@
         <v>78</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -11232,7 +11198,7 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>78</v>
@@ -11243,10 +11209,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11286,7 +11252,7 @@
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>78</v>
@@ -11360,10 +11326,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11374,7 +11340,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11386,13 +11352,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>205</v>
+        <v>481</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11475,20 +11441,20 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>89</v>
@@ -11503,13 +11469,13 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>134</v>
+        <v>440</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>135</v>
+        <v>484</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>136</v>
+        <v>442</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11592,10 +11558,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11707,10 +11673,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11718,10 +11684,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>79</v>
+        <v>447</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11822,12 +11788,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C82" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>449</v>
+      </c>
       <c r="D82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11848,24 +11816,22 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>78</v>
@@ -11907,19 +11873,19 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -11928,7 +11894,7 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11939,10 +11905,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11965,13 +11931,13 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>482</v>
+        <v>155</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>465</v>
+        <v>156</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>466</v>
+        <v>157</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12022,7 +11988,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12034,7 +12000,7 @@
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -12043,7 +12009,7 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -12054,10 +12020,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>484</v>
+        <v>453</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12065,10 +12031,10 @@
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -12080,24 +12046,22 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>485</v>
+        <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>78</v>
@@ -12127,31 +12091,31 @@
         <v>78</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -12160,7 +12124,7 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -12171,10 +12135,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>487</v>
+        <v>455</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12182,10 +12146,10 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>78</v>
@@ -12197,22 +12161,24 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>488</v>
+        <v>103</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>465</v>
+        <v>166</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N85" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>78</v>
@@ -12254,10 +12220,10 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>89</v>
@@ -12266,7 +12232,7 @@
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -12286,14 +12252,12 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>490</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>78</v>
       </c>
@@ -12314,13 +12278,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>447</v>
+        <v>109</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>491</v>
+        <v>458</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12332,7 +12296,7 @@
         <v>78</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>78</v>
+        <v>492</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>78</v>
@@ -12347,13 +12311,11 @@
         <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="Y86" s="2"/>
       <c r="Z86" t="s" s="2">
-        <v>78</v>
+        <v>461</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
@@ -12371,19 +12333,19 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12392,7 +12354,7 @@
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12403,12 +12365,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12429,13 +12393,13 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>156</v>
+        <v>464</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12486,19 +12450,19 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
@@ -12507,7 +12471,7 @@
         <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>78</v>
@@ -12518,10 +12482,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12529,10 +12493,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>454</v>
+        <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
@@ -12544,13 +12508,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12589,31 +12553,31 @@
         <v>78</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
@@ -12622,7 +12586,7 @@
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12633,23 +12597,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B89" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="C89" t="s" s="2">
-        <v>456</v>
-      </c>
+      <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -12706,16 +12668,16 @@
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF89" t="s" s="2">
         <v>163</v>
@@ -12750,10 +12712,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12761,7 +12723,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>89</v>
@@ -12776,22 +12738,24 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>78</v>
@@ -12833,10 +12797,10 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>89</v>
@@ -12854,7 +12818,7 @@
         <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>78</v>
@@ -12865,10 +12829,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12879,7 +12843,7 @@
         <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
@@ -12891,13 +12855,13 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>135</v>
+        <v>458</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>136</v>
+        <v>459</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12936,31 +12900,31 @@
         <v>78</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -12969,7 +12933,7 @@
         <v>78</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -12980,12 +12944,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="C92" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="D92" t="s" s="2">
         <v>78</v>
       </c>
@@ -13006,24 +12972,22 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>456</v>
+        <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>78</v>
@@ -13065,19 +13029,19 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
@@ -13086,7 +13050,7 @@
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -13097,10 +13061,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13123,13 +13087,13 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>465</v>
+        <v>156</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>466</v>
+        <v>157</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13141,7 +13105,7 @@
         <v>78</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>499</v>
+        <v>78</v>
       </c>
       <c r="T93" t="s" s="2">
         <v>78</v>
@@ -13156,11 +13120,13 @@
         <v>78</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y93" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z93" t="s" s="2">
-        <v>468</v>
+        <v>78</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -13178,7 +13144,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13190,7 +13156,7 @@
         <v>78</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
@@ -13199,7 +13165,7 @@
         <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -13215,9 +13181,7 @@
       <c r="B94" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="C94" t="s" s="2">
-        <v>470</v>
-      </c>
+      <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
         <v>78</v>
       </c>
@@ -13226,7 +13190,7 @@
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
@@ -13241,7 +13205,7 @@
         <v>134</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>471</v>
+        <v>135</v>
       </c>
       <c r="M94" t="s" s="2">
         <v>136</v>
@@ -13283,16 +13247,16 @@
         <v>78</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF94" t="s" s="2">
         <v>163</v>
@@ -13330,7 +13294,7 @@
         <v>501</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13338,7 +13302,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>89</v>
@@ -13353,22 +13317,24 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>78</v>
+        <v>470</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>78</v>
@@ -13410,10 +13376,10 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>89</v>
@@ -13431,7 +13397,7 @@
         <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13445,7 +13411,7 @@
         <v>502</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13456,7 +13422,7 @@
         <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>78</v>
@@ -13468,13 +13434,13 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>134</v>
+        <v>475</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>135</v>
+        <v>458</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>136</v>
+        <v>459</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13513,31 +13479,31 @@
         <v>78</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
@@ -13546,7 +13512,7 @@
         <v>78</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>78</v>
@@ -13560,7 +13526,7 @@
         <v>503</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>462</v>
+        <v>477</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13600,7 +13566,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>78</v>
@@ -13677,7 +13643,7 @@
         <v>504</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13688,7 +13654,7 @@
         <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>78</v>
@@ -13700,13 +13666,13 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>205</v>
+        <v>481</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>465</v>
+        <v>458</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13792,17 +13758,15 @@
         <v>505</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>477</v>
-      </c>
+        <v>505</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
         <v>89</v>
@@ -13814,18 +13778,20 @@
         <v>78</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>135</v>
+        <v>506</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>507</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>78</v>
@@ -13874,19 +13840,19 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>163</v>
+        <v>509</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>78</v>
+        <v>510</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>78</v>
@@ -13895,7 +13861,7 @@
         <v>78</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13906,10 +13872,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>506</v>
+        <v>511</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>458</v>
+        <v>511</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13929,18 +13895,20 @@
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>156</v>
+        <v>512</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>513</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>514</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -13965,13 +13933,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>78</v>
+        <v>423</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>78</v>
+        <v>515</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>78</v>
+        <v>516</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -13989,7 +13957,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>158</v>
+        <v>517</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14001,7 +13969,7 @@
         <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>78</v>
@@ -14010,7 +13978,7 @@
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -14021,10 +13989,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>460</v>
+        <v>518</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14035,7 +14003,7 @@
         <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -14044,18 +14012,20 @@
         <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>134</v>
+        <v>186</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>135</v>
+        <v>519</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14092,31 +14062,31 @@
         <v>78</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>163</v>
+        <v>522</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>78</v>
@@ -14125,7 +14095,7 @@
         <v>78</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>78</v>
+        <v>523</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -14136,10 +14106,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>462</v>
+        <v>524</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14147,7 +14117,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>89</v>
@@ -14159,19 +14129,19 @@
         <v>78</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>166</v>
+        <v>525</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>167</v>
+        <v>526</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>168</v>
+        <v>527</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14179,7 +14149,7 @@
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>78</v>
@@ -14221,10 +14191,10 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>170</v>
+        <v>528</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>89</v>
@@ -14233,7 +14203,7 @@
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
@@ -14251,12 +14221,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
-        <v>509</v>
+        <v>529</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>464</v>
+        <v>529</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14270,22 +14240,22 @@
         <v>89</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>482</v>
+        <v>530</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>465</v>
+        <v>531</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>466</v>
+        <v>532</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14336,13 +14306,13 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>177</v>
+        <v>529</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>78</v>
@@ -14351,13 +14321,13 @@
         <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>132</v>
+        <v>535</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>78</v>
@@ -14368,10 +14338,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>510</v>
+        <v>536</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>484</v>
+        <v>536</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14379,10 +14349,10 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>78</v>
@@ -14394,24 +14364,22 @@
         <v>78</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>166</v>
+        <v>537</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>538</v>
+      </c>
+      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>485</v>
+        <v>78</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>78</v>
@@ -14429,13 +14397,13 @@
         <v>78</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>78</v>
+        <v>539</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>78</v>
+        <v>540</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>78</v>
@@ -14453,28 +14421,28 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>170</v>
+        <v>536</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>78</v>
+        <v>541</v>
       </c>
       <c r="AL104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>132</v>
+        <v>542</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>78</v>
@@ -14483,12 +14451,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>511</v>
+        <v>543</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>487</v>
+        <v>543</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14499,10 +14467,10 @@
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>78</v>
@@ -14511,13 +14479,13 @@
         <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>488</v>
+        <v>544</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>465</v>
+        <v>545</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>466</v>
+        <v>546</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14568,13 +14536,13 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>177</v>
+        <v>543</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>78</v>
@@ -14583,7 +14551,7 @@
         <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>78</v>
+        <v>547</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>78</v>
@@ -14600,10 +14568,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>512</v>
+        <v>548</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14620,28 +14588,30 @@
         <v>78</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>155</v>
+        <v>284</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>514</v>
+        <v>550</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>515</v>
+        <v>551</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q106" s="2"/>
+      <c r="Q106" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="R106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14685,7 +14655,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>516</v>
+        <v>548</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14694,7 +14664,7 @@
         <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>517</v>
+        <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>101</v>
@@ -14703,7 +14673,7 @@
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>78</v>
+        <v>553</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>132</v>
@@ -14717,10 +14687,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>518</v>
+        <v>554</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>518</v>
+        <v>554</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14731,7 +14701,7 @@
         <v>79</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>78</v>
@@ -14740,20 +14710,18 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>519</v>
+        <v>555</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>521</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -14778,13 +14746,13 @@
         <v>78</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>430</v>
+        <v>209</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>522</v>
+        <v>557</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>523</v>
+        <v>558</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
@@ -14802,13 +14770,13 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>524</v>
+        <v>554</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>78</v>
@@ -14834,10 +14802,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>525</v>
+        <v>559</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>525</v>
+        <v>559</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14848,7 +14816,7 @@
         <v>79</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>78</v>
@@ -14857,20 +14825,18 @@
         <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>186</v>
+        <v>407</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>526</v>
+        <v>560</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -14919,19 +14885,19 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>101</v>
+        <v>562</v>
       </c>
       <c r="AK108" t="s" s="2">
         <v>78</v>
@@ -14940,7 +14906,7 @@
         <v>78</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>530</v>
+        <v>132</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>78</v>
@@ -14951,10 +14917,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14974,20 +14940,18 @@
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
         <v>155</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>532</v>
+        <v>156</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>78</v>
@@ -15036,7 +15000,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>535</v>
+        <v>158</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15048,7 +15012,7 @@
         <v>78</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>78</v>
@@ -15057,7 +15021,7 @@
         <v>78</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>78</v>
@@ -15066,43 +15030,45 @@
         <v>78</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>536</v>
+        <v>564</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>537</v>
+        <v>134</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>538</v>
+        <v>226</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>78</v>
@@ -15151,7 +15117,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>536</v>
+        <v>163</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15163,16 +15129,16 @@
         <v>78</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>540</v>
+        <v>78</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>541</v>
+        <v>78</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>542</v>
+        <v>159</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>78</v>
@@ -15183,14 +15149,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>543</v>
+        <v>565</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15203,22 +15169,26 @@
         <v>78</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>544</v>
+        <v>417</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O111" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P111" t="s" s="2">
         <v>78</v>
       </c>
@@ -15242,13 +15212,13 @@
         <v>78</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>546</v>
+        <v>78</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>547</v>
+        <v>78</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>78</v>
@@ -15266,7 +15236,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>543</v>
+        <v>419</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -15278,16 +15248,16 @@
         <v>78</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>549</v>
+        <v>132</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>78</v>
@@ -15296,12 +15266,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15312,10 +15282,10 @@
         <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H112" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I112" t="s" s="2">
         <v>78</v>
@@ -15324,13 +15294,13 @@
         <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>551</v>
+        <v>155</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15381,13 +15351,13 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>78</v>
@@ -15396,10 +15366,10 @@
         <v>101</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>554</v>
+        <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>78</v>
+        <v>569</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>132</v>
@@ -15413,10 +15383,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15433,30 +15403,26 @@
         <v>78</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>281</v>
+        <v>103</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q113" t="s" s="2">
-        <v>559</v>
-      </c>
+      <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
         <v>78</v>
       </c>
@@ -15500,7 +15466,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15518,7 +15484,7 @@
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>560</v>
+        <v>78</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>132</v>
@@ -15532,10 +15498,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15546,7 +15512,7 @@
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>78</v>
@@ -15558,13 +15524,13 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>205</v>
+        <v>317</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15591,13 +15557,13 @@
         <v>78</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>564</v>
+        <v>78</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>565</v>
+        <v>78</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>78</v>
@@ -15615,13 +15581,13 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>78</v>
@@ -15633,7 +15599,7 @@
         <v>78</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>78</v>
+        <v>576</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>132</v>
@@ -15647,10 +15613,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15661,7 +15627,7 @@
         <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>78</v>
@@ -15673,13 +15639,13 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>414</v>
+        <v>317</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -15730,25 +15696,25 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>569</v>
+        <v>101</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>78</v>
+        <v>580</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>132</v>
@@ -15762,10 +15728,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15776,7 +15742,7 @@
         <v>79</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>78</v>
@@ -15788,13 +15754,13 @@
         <v>78</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>155</v>
+        <v>205</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>156</v>
+        <v>582</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>157</v>
+        <v>583</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15821,13 +15787,13 @@
         <v>78</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>78</v>
+        <v>584</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>78</v>
+        <v>585</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>78</v>
@@ -15845,28 +15811,28 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>158</v>
+        <v>581</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK116" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>78</v>
+        <v>586</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>78</v>
@@ -15877,21 +15843,21 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>571</v>
+        <v>587</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>78</v>
@@ -15903,17 +15869,15 @@
         <v>78</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>134</v>
+        <v>205</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>226</v>
+        <v>588</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>78</v>
@@ -15938,13 +15902,13 @@
         <v>78</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>78</v>
+        <v>590</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>78</v>
+        <v>591</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>78</v>
@@ -15962,19 +15926,19 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>163</v>
+        <v>587</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>78</v>
@@ -15983,7 +15947,7 @@
         <v>78</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>78</v>
@@ -15994,14 +15958,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>572</v>
+        <v>592</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>423</v>
+        <v>78</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -16014,26 +15978,24 @@
         <v>78</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>134</v>
+        <v>407</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>424</v>
+        <v>593</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>425</v>
+        <v>594</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>78</v>
       </c>
@@ -16081,7 +16043,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>426</v>
+        <v>592</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16093,16 +16055,16 @@
         <v>78</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>78</v>
+        <v>596</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>132</v>
+        <v>597</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>78</v>
@@ -16113,10 +16075,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>573</v>
+        <v>598</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>573</v>
+        <v>598</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16142,10 +16104,10 @@
         <v>155</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>574</v>
+        <v>156</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>575</v>
+        <v>157</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16196,7 +16158,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>573</v>
+        <v>158</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16208,16 +16170,16 @@
         <v>78</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>576</v>
+        <v>78</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>78</v>
@@ -16228,21 +16190,21 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>577</v>
+        <v>599</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>577</v>
+        <v>599</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>78</v>
@@ -16254,15 +16216,17 @@
         <v>78</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>578</v>
+        <v>226</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>78</v>
@@ -16311,19 +16275,19 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>577</v>
+        <v>163</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK120" t="s" s="2">
         <v>78</v>
@@ -16332,7 +16296,7 @@
         <v>78</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>78</v>
@@ -16343,42 +16307,46 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
-        <v>78</v>
+        <v>416</v>
       </c>
       <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I121" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J121" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>324</v>
+        <v>134</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>581</v>
+        <v>417</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="O121" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="P121" t="s" s="2">
         <v>78</v>
       </c>
@@ -16426,25 +16394,25 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>580</v>
+        <v>419</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>583</v>
+        <v>78</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>132</v>
@@ -16458,10 +16426,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16484,13 +16452,13 @@
         <v>78</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>586</v>
+        <v>603</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16541,7 +16509,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>584</v>
+        <v>601</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16559,10 +16527,10 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>132</v>
+        <v>323</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>78</v>
@@ -16573,10 +16541,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16587,7 +16555,7 @@
         <v>79</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>78</v>
@@ -16599,13 +16567,13 @@
         <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>205</v>
+        <v>606</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>589</v>
+        <v>607</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16632,13 +16600,13 @@
         <v>78</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>591</v>
+        <v>78</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>592</v>
+        <v>78</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>78</v>
@@ -16656,13 +16624,13 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>588</v>
+        <v>605</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>78</v>
@@ -16674,10 +16642,10 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>593</v>
+        <v>609</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>132</v>
+        <v>610</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>78</v>
@@ -16688,10 +16656,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16714,13 +16682,13 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>205</v>
+        <v>284</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>596</v>
+        <v>613</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16747,13 +16715,13 @@
         <v>78</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>209</v>
+        <v>78</v>
       </c>
       <c r="Y124" t="s" s="2">
-        <v>597</v>
+        <v>78</v>
       </c>
       <c r="Z124" t="s" s="2">
-        <v>598</v>
+        <v>78</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>78</v>
@@ -16771,7 +16739,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16789,10 +16757,10 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>78</v>
+        <v>614</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>132</v>
+        <v>615</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>78</v>
@@ -16801,12 +16769,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
-        <v>599</v>
+        <v>616</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>599</v>
+        <v>616</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16820,7 +16788,7 @@
         <v>80</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>78</v>
@@ -16829,17 +16797,15 @@
         <v>78</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>600</v>
+        <v>617</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -16888,7 +16854,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>599</v>
+        <v>616</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16906,10 +16872,10 @@
         <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>603</v>
+        <v>78</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>604</v>
+        <v>132</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>78</v>
@@ -16920,10 +16886,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17035,10 +17001,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17152,14 +17118,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -17181,10 +17147,10 @@
         <v>134</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="N128" t="s" s="2">
         <v>182</v>
@@ -17239,7 +17205,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17271,10 +17237,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17297,13 +17263,13 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>324</v>
+        <v>155</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>610</v>
+        <v>624</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17330,13 +17296,11 @@
         <v>78</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>78</v>
+        <v>625</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>78</v>
@@ -17354,7 +17318,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17372,10 +17336,10 @@
         <v>78</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>611</v>
+        <v>78</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>330</v>
+        <v>132</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>78</v>
@@ -17386,10 +17350,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17412,13 +17376,13 @@
         <v>78</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>613</v>
+        <v>368</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17469,7 +17433,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17487,10 +17451,10 @@
         <v>78</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>616</v>
+        <v>78</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>617</v>
+        <v>132</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>78</v>
@@ -17501,10 +17465,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17515,7 +17479,7 @@
         <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>78</v>
@@ -17527,13 +17491,13 @@
         <v>78</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>281</v>
+        <v>205</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17560,13 +17524,13 @@
         <v>78</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>78</v>
+        <v>209</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>78</v>
+        <v>632</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>78</v>
+        <v>633</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>78</v>
@@ -17584,13 +17548,13 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>78</v>
@@ -17602,10 +17566,10 @@
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>621</v>
+        <v>78</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>622</v>
+        <v>132</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -17614,12 +17578,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17627,13 +17591,13 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>78</v>
@@ -17642,15 +17606,17 @@
         <v>78</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>414</v>
+        <v>635</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>637</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>638</v>
+      </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -17687,25 +17653,23 @@
         <v>78</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>639</v>
+      </c>
+      <c r="AC132" s="2"/>
       <c r="AD132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>78</v>
@@ -17729,14 +17693,16 @@
         <v>78</v>
       </c>
     </row>
-    <row r="133" hidden="true">
+    <row r="133">
       <c r="A133" t="s" s="2">
-        <v>626</v>
+        <v>640</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C133" s="2"/>
+        <v>634</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="D133" t="s" s="2">
         <v>78</v>
       </c>
@@ -17748,7 +17714,7 @@
         <v>89</v>
       </c>
       <c r="H133" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I133" t="s" s="2">
         <v>78</v>
@@ -17757,15 +17723,17 @@
         <v>78</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>155</v>
+        <v>642</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>156</v>
+        <v>643</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>637</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>638</v>
+      </c>
       <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -17814,10 +17782,10 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>158</v>
+        <v>634</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>89</v>
@@ -17826,7 +17794,7 @@
         <v>78</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK133" t="s" s="2">
         <v>78</v>
@@ -17835,7 +17803,7 @@
         <v>78</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>78</v>
@@ -17846,21 +17814,21 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>627</v>
+        <v>644</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>627</v>
+        <v>644</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>179</v>
+        <v>78</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>78</v>
@@ -17872,16 +17840,16 @@
         <v>78</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>134</v>
+        <v>635</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>226</v>
+        <v>645</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>227</v>
+        <v>646</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>182</v>
+        <v>638</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -17931,19 +17899,19 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>163</v>
+        <v>644</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>78</v>
@@ -17952,830 +17920,17 @@
         <v>78</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO134" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="P135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
-      <c r="P136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="Y136" s="2"/>
-      <c r="Z136" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
-      <c r="P137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="138" hidden="true">
-      <c r="A138" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
-      <c r="P138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="139" hidden="true">
-      <c r="A139" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="O139" s="2"/>
-      <c r="P139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AC139" s="2"/>
-      <c r="AD139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="C140" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="D140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="O140" s="2"/>
-      <c r="P140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="141" hidden="true">
-      <c r="A141" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="O141" s="2"/>
-      <c r="P141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO141" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO141">
+  <autoFilter ref="A1:AO134">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18785,7 +17940,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI140">
+  <conditionalFormatting sqref="A2:AI133">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-04T15:31:02+00:00</t>
+    <t>2026-06-16T14:27:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:27:29+00:00</t>
+    <t>2026-06-18T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-immunization-document.xlsx
+++ b/main/ig/StructureDefinition-fr-immunization-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:40:49+00:00</t>
+    <t>2026-06-22T09:35:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
